--- a/création des scénarios.xlsx
+++ b/création des scénarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED44925-3A34-4AED-B8B4-4E1AD8BA7E49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6712C1B7-E642-4082-B34E-40DA6790B53D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6060" firstSheet="1" activeTab="4" xr2:uid="{AD25C4C4-CDAB-475A-A223-6BD98AE97C2F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6060" activeTab="6" xr2:uid="{AD25C4C4-CDAB-475A-A223-6BD98AE97C2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="minEQ" sheetId="3" r:id="rId3"/>
     <sheet name="minHH" sheetId="5" r:id="rId4"/>
     <sheet name="Feuil6" sheetId="6" r:id="rId5"/>
+    <sheet name="bi-objectif" sheetId="7" r:id="rId6"/>
+    <sheet name="tri-objectif" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="108">
   <si>
     <t>Tableau des scénarios</t>
   </si>
@@ -163,9 +165,6 @@
 - IC existant pour les buildings</t>
   </si>
   <si>
-    <t>tout vers AD-c nouveau</t>
-  </si>
-  <si>
     <t>sc_reel_civic_led</t>
   </si>
   <si>
@@ -208,12 +207,6 @@
     <t>Total ecosystem quality (PDF.m2.yr)</t>
   </si>
   <si>
-    <t>AD-b existant et AD-b nouveau</t>
-  </si>
-  <si>
-    <t>AD-b existant puis AD-c existant</t>
-  </si>
-  <si>
     <t>sc_reel_civic_led_EQ</t>
   </si>
   <si>
@@ -226,12 +219,6 @@
     <t>civic_ss_inv_HH</t>
   </si>
   <si>
-    <t>AD-C existant puis IC existant</t>
-  </si>
-  <si>
-    <t>AD-c nouveau</t>
-  </si>
-  <si>
     <t>Carbon</t>
   </si>
   <si>
@@ -281,6 +268,99 @@
   </si>
   <si>
     <t xml:space="preserve">AD-b existant (build) et HC </t>
+  </si>
+  <si>
+    <t>Carb</t>
+  </si>
+  <si>
+    <t>avec investissement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC et AD-b existant </t>
+  </si>
+  <si>
+    <t>-EQ : 0.25, HH : 0.75</t>
+  </si>
+  <si>
+    <t>-EQ : 0.5, HH : 0.5</t>
+  </si>
+  <si>
+    <t>Scénario</t>
+  </si>
+  <si>
+    <t>-EQ : 0.75, HH : 0.25</t>
+  </si>
+  <si>
+    <t>-EQ : 0.25, HH : 0.75, Carb : 0</t>
+  </si>
+  <si>
+    <t>AD-b nouveau +AD-b existant</t>
+  </si>
+  <si>
+    <t>-EQ : 0.75, HH : 0.25, Carb : 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-EQ : 0.5, HH : 0.5, Carb : 0 </t>
+  </si>
+  <si>
+    <t>-EQ : 0, HH : 0.75, Carb : 0.25</t>
+  </si>
+  <si>
+    <t>AD-c nouveau + HC</t>
+  </si>
+  <si>
+    <t>-EQ : 0.75, HH : 0, Carb : 0.25</t>
+  </si>
+  <si>
+    <t>-EQ : 0, HH : 0.25, Carb : 0.75</t>
+  </si>
+  <si>
+    <t>-EQ : 0.25, HH : 0, Carb : 0.75</t>
+  </si>
+  <si>
+    <t>-EQ : 0, HH : 0.5, Carb : 0.5</t>
+  </si>
+  <si>
+    <t>-EQ : 0.5, HH : 0, Carb : 0.5</t>
+  </si>
+  <si>
+    <t>-EQ : 0.33, HH : 0.33, Carb : 0.33</t>
+  </si>
+  <si>
+    <t>-EQ : 0.99/2 HH : 0.99/2, Carb : 0.01</t>
+  </si>
+  <si>
+    <t>-EQ : 0.999/2 HH : 0.999/2, Carb : 0.001</t>
+  </si>
+  <si>
+    <t>AD-c existant+ HC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Carb : 0.0015</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Carb : 0.002</t>
+  </si>
+  <si>
+    <t>AD-C existant et HC</t>
+  </si>
+  <si>
+    <t>AD-c nouveau et HC</t>
+  </si>
+  <si>
+    <t>AD-f</t>
+  </si>
+  <si>
+    <t>AD-e et HC</t>
+  </si>
+  <si>
+    <t>HC + AD-e</t>
+  </si>
+  <si>
+    <t>Sans investissement</t>
+  </si>
+  <si>
+    <t>sans_investissement</t>
   </si>
 </sst>
 </file>
@@ -291,7 +371,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.00000E+00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +391,19 @@
       <color rgb="FF000000"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -426,7 +519,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -453,6 +546,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -485,39 +583,19 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.6683921429941181E-2"/>
+          <c:y val="1.2353965428351864E-2"/>
+          <c:w val="0.94693479803372238"/>
+          <c:h val="0.88254668636018563"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -538,7 +616,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -549,16 +627,74 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent4"/>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Feuil6!$B$9:$D$9</c:f>
@@ -586,10 +722,10 @@
                   <c:v>3.8833510370696905E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.45536603816514926</c:v>
+                  <c:v>0.82451755791110892</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9999999999999822E-2</c:v>
+                  <c:v>0.49197860962566836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -597,7 +733,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A55E-436E-A7A0-C28712E05AEF}"/>
+              <c16:uniqueId val="{00000000-9744-41D7-9C2F-AC4E74ED7F0B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -616,11 +752,10 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd" cmpd="sng">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:prstDash val="lgDash"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -630,16 +765,74 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent5"/>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Feuil6!$B$9:$D$9</c:f>
@@ -667,7 +860,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.67779746694881549</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -678,7 +871,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A55E-436E-A7A0-C28712E05AEF}"/>
+              <c16:uniqueId val="{00000001-9744-41D7-9C2F-AC4E74ED7F0B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -699,7 +892,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -720,6 +913,64 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Feuil6!$B$9:$D$9</c:f>
@@ -747,10 +998,10 @@
                   <c:v>4.1366440169448973E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.36699372985597445</c:v>
+                  <c:v>0.7960437763223126</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.46524064171122997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -758,7 +1009,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A55E-436E-A7A0-C28712E05AEF}"/>
+              <c16:uniqueId val="{00000002-9744-41D7-9C2F-AC4E74ED7F0B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -779,28 +1030,86 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:prstDash val="lgDash"/>
+              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="triangle"/>
+            <c:size val="12"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent4"/>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Feuil6!$B$9:$D$9</c:f>
@@ -831,7 +1140,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.37999999999999989</c:v>
+                  <c:v>0.66844919786096257</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -839,13 +1148,154 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A55E-436E-A7A0-C28712E05AEF}"/>
+              <c16:uniqueId val="{00000003-9744-41D7-9C2F-AC4E74ED7F0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil6!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>minEQ_inv</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="14"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:alpha val="94000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil6!$B$9:$D$9</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Carbon</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>EQ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>HH</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil6!$B$14:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.70140960584572098</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28342245989304776</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9744-41D7-9C2F-AC4E74ED7F0B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
-          <c:order val="4"/>
+          <c:order val="5"/>
           <c:tx>
             <c:strRef>
               <c:f>Feuil6!$A$15</c:f>
@@ -858,9 +1308,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
               <a:round/>
@@ -868,20 +1318,78 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="triangle"/>
+            <c:size val="12"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent3"/>
+                  <a:schemeClr val="accent6"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Feuil6!$B$9:$D$9</c:f>
@@ -906,10 +1414,10 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4.1366440169448973E-2</c:v>
+                  <c:v>0.14158981947414501</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.36699372985597445</c:v>
+                  <c:v>0.11677650936152997</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -920,13 +1428,14 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000A-A55E-436E-A7A0-C28712E05AEF}"/>
+              <c16:uniqueId val="{00000009-9744-41D7-9C2F-AC4E74ED7F0B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -934,11 +1443,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="860243648"/>
-        <c:axId val="1986738336"/>
+        <c:axId val="611429712"/>
+        <c:axId val="527248528"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="860243648"/>
+        <c:axId val="611429712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -958,16 +1467,11 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
+          <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
             <a:round/>
           </a:ln>
           <a:effectLst/>
@@ -992,7 +1496,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1986738336"/>
+        <c:crossAx val="527248528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1000,7 +1504,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1986738336"/>
+        <c:axId val="527248528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1010,7 +1514,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="860243648"/>
+        <c:crossAx val="611429712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1055,13 +1559,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -1644,23 +2141,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>311661</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>107258</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>31889</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>85307</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>400326</xdr:colOff>
+      <xdr:colOff>693393</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>124238</xdr:rowOff>
+      <xdr:rowOff>151845</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Graphique 3">
+        <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CAE72FF-F427-430A-8A8E-FAF3A575F794}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{635F2603-10E8-4538-A9C7-27F8398BB267}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2268,7 +2765,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>38</v>
@@ -2300,10 +2797,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <v>0.2</v>
@@ -2321,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="16">
         <v>76600.100000000006</v>
@@ -2332,7 +2829,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>40</v>
@@ -2367,7 +2864,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>0.8</v>
@@ -2385,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J5" s="16">
         <v>-907734.15</v>
@@ -2399,10 +2896,10 @@
     </row>
     <row r="6" spans="1:12" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -2420,7 +2917,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J6" s="19">
         <v>-892871.22</v>
@@ -2445,19 +2942,19 @@
     <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>
       <c r="B10" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="14"/>
       <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
         <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2504,13 +3001,13 @@
         <v>27</v>
       </c>
       <c r="K1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -2518,7 +3015,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>38</v>
@@ -2548,10 +3045,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <v>0.2</v>
@@ -2577,7 +3074,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>40</v>
@@ -2609,7 +3106,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>0.8</v>
@@ -2627,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K5" s="16">
         <v>-534021.30000000005</v>
@@ -2641,10 +3138,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -2662,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K6" s="16">
         <v>-534021.30000000005</v>
@@ -2718,13 +3215,13 @@
         <v>27</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="29" x14ac:dyDescent="0.35">
@@ -2732,7 +3229,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>38</v>
@@ -2760,10 +3257,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <v>0.2</v>
@@ -2787,7 +3284,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>40</v>
@@ -2817,7 +3314,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>0.8</v>
@@ -2835,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J5" s="17">
         <v>-6.02</v>
@@ -2850,10 +3347,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -2871,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J6" s="17">
         <v>-6.02</v>
@@ -2904,21 +3401,21 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B2" s="17">
         <f>minCO2!J6</f>
@@ -2933,12 +3430,12 @@
         <v>-5.97</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B3" s="17">
         <f>minEQ!L6</f>
@@ -2953,12 +3450,12 @@
         <v>-5.0199999999999996</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B4" s="17">
         <f>minHH!K6</f>
@@ -2973,86 +3470,83 @@
         <v>-6.02</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="17">
+      <c r="A5" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="24">
         <f>minCO2!J5</f>
         <v>-907734.15</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="24">
         <f>minCO2!L5</f>
         <v>-462294.08</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="24">
         <f>minCO2!K5</f>
         <v>-5.64</v>
       </c>
-      <c r="F5" t="s">
-        <v>43</v>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="17">
-        <f>minEQ!L5</f>
-        <v>-524999.5</v>
-      </c>
-      <c r="C6" s="17">
-        <f>minEQ!K5</f>
-        <v>-534021.30000000005</v>
-      </c>
-      <c r="D6" s="17">
-        <f>minEQ!M5</f>
-        <v>-5.0199999999999996</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
+      <c r="A6" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="24">
+        <v>-639280.39</v>
+      </c>
+      <c r="C6" s="24">
+        <v>-684909.4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>-6.36</v>
+      </c>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="17">
-        <f>minHH!K5</f>
-        <v>-891901.78</v>
-      </c>
-      <c r="C7" s="17">
-        <f>minHH!L5</f>
-        <v>-507697.86</v>
-      </c>
-      <c r="D7" s="17">
-        <f>minHH!J5</f>
-        <v>-6.02</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
+      <c r="A7" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="24">
+        <v>-853542.82</v>
+      </c>
+      <c r="C7" s="24">
+        <v>-658913.16</v>
+      </c>
+      <c r="D7" s="24">
+        <v>-6.89</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B10" s="17">
         <f>(B2-MIN(B$2:B$7))/(MAX(B$2:B$7)-MIN(B$2:B$7))</f>
@@ -3060,19 +3554,19 @@
       </c>
       <c r="C10" s="17">
         <f>(C2-MIN(C$2:C$7))/(MAX(C$2:C$7)-MIN(C$2:C$7))</f>
-        <v>0.45536603816514926</v>
+        <v>0.82451755791110892</v>
       </c>
       <c r="D10" s="17">
         <f>(D2-MIN(D$2:D$7))/(MAX(D$2:D$7)-MIN(D$2:D$7))</f>
-        <v>4.9999999999999822E-2</v>
+        <v>0.49197860962566836</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B11" s="17">
         <f t="shared" ref="B11:D15" si="0">(B3-MIN(B$2:B$7))/(MAX(B$2:B$7)-MIN(B$2:B$7))</f>
@@ -3080,19 +3574,19 @@
       </c>
       <c r="C11" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.67779746694881549</v>
       </c>
       <c r="D11" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B12" s="17">
         <f t="shared" si="0"/>
@@ -3100,19 +3594,19 @@
       </c>
       <c r="C12" s="17">
         <f t="shared" si="0"/>
-        <v>0.36699372985597445</v>
+        <v>0.7960437763223126</v>
       </c>
       <c r="D12" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.46524064171122997</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B13" s="17">
         <f t="shared" si="0"/>
@@ -3124,19 +3618,19 @@
       </c>
       <c r="D13" s="17">
         <f t="shared" si="0"/>
-        <v>0.37999999999999989</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
+        <v>0.66844919786096257</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B14" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.70140960584572098</v>
       </c>
       <c r="C14" s="17">
         <f t="shared" si="0"/>
@@ -3144,30 +3638,30 @@
       </c>
       <c r="D14" s="17">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
+        <v>0.28342245989304776</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B15" s="17">
         <f t="shared" si="0"/>
-        <v>4.1366440169448973E-2</v>
+        <v>0.14158981947414501</v>
       </c>
       <c r="C15" s="17">
         <f t="shared" si="0"/>
-        <v>0.36699372985597445</v>
+        <v>0.11677650936152997</v>
       </c>
       <c r="D15" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" t="s">
-        <v>64</v>
+      <c r="F15" s="21" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
@@ -3182,6 +3676,429 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F3D33A7-A91A-4E9E-88BE-5C76E165C30A}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="23">
+        <v>-659098.98</v>
+      </c>
+      <c r="D2" s="23">
+        <v>-6.89</v>
+      </c>
+      <c r="E2" s="23">
+        <v>-857133.79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="21"/>
+      <c r="B3" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="23">
+        <v>-660904</v>
+      </c>
+      <c r="D3" s="23">
+        <v>-6.88</v>
+      </c>
+      <c r="E3" s="23">
+        <v>-852209.13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="21"/>
+      <c r="B4" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="23">
+        <v>-684846.59</v>
+      </c>
+      <c r="D4" s="23">
+        <v>-6.38</v>
+      </c>
+      <c r="E4" s="23">
+        <v>-645332.42000000004</v>
+      </c>
+      <c r="F4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84745C5C-FC0B-4996-84A9-EE8F97DDA6E0}">
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="27.6328125" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="17">
+        <v>-231080.28</v>
+      </c>
+      <c r="E2" s="17">
+        <v>-0.11</v>
+      </c>
+      <c r="F2" s="17">
+        <f>-151661.15</f>
+        <v>-151661.15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="17">
+        <v>-231080.28</v>
+      </c>
+      <c r="E3" s="17">
+        <v>-0.11</v>
+      </c>
+      <c r="F3" s="17">
+        <f>-151661.15</f>
+        <v>-151661.15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="17">
+        <v>-231080.28</v>
+      </c>
+      <c r="E4" s="17">
+        <v>-0.11</v>
+      </c>
+      <c r="F4" s="17">
+        <f>-151661.15</f>
+        <v>-151661.15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E5" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F5" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E6" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F6" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E7" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F7" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E8" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F8" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E9" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F9" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9">
+        <f>282500/36529</f>
+        <v>7.7335815379561446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E10" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F10" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E11" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F11" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B13">
+        <v>13</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="17">
+        <v>126584.77</v>
+      </c>
+      <c r="E13" s="17">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F13" s="17">
+        <v>-911649.08</v>
+      </c>
+      <c r="G13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B15">
+        <v>15</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="17">
+        <v>37402.480000000003</v>
+      </c>
+      <c r="E15" s="17">
+        <v>1.29</v>
+      </c>
+      <c r="F15" s="17">
+        <v>-894066.33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C16" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="17">
+        <v>37402.480000000003</v>
+      </c>
+      <c r="E16" s="17">
+        <v>1.29</v>
+      </c>
+      <c r="F16" s="17">
+        <v>-894066.33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C17" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="17">
+        <v>37402.480000000003</v>
+      </c>
+      <c r="E17" s="17">
+        <v>1.29</v>
+      </c>
+      <c r="F17" s="17">
+        <v>-894066.33</v>
+      </c>
+      <c r="G17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>
 </worksheet>
 </file>